--- a/education_surveys/019_ixodes_ricinus_knowledge_quiz--education_surveys.xlsx
+++ b/education_surveys/019_ixodes_ricinus_knowledge_quiz--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1067,34 +1067,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_page_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ornithoecchus</t>
+          <t>aedes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ornithoecchus</t>
+          <t>Aedes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_page_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ixodes</t>
+          <t>amblyomma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ixodes</t>
+          <t>Amblyomma</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>aedes</t>
+          <t>ixodes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aedes</t>
+          <t>Ixodes</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>amblyomma</t>
+          <t>haemaphodonta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amblyomma</t>
+          <t>Haemaphodonta</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ixodes</t>
+          <t>ornithoecchus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ixodes</t>
+          <t>Ornithoecchus</t>
         </is>
       </c>
     </row>
@@ -1157,46 +1157,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>haemaphodonta</t>
+          <t>ornithonyssus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Haemaphodonta</t>
+          <t>Ornithonyssus</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ornithoecchus</t>
+          <t>larva</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ornithoecchus</t>
+          <t>Larva</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ornithonyssus</t>
+          <t>nymph</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ornithonyssus</t>
+          <t>Nymph</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>larva</t>
+          <t>larva_and_nymph</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Larva</t>
+          <t>larva and nymph</t>
         </is>
       </c>
     </row>
@@ -1225,46 +1225,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nymph</t>
+          <t>larva,_nymph,_and_adult</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nymph</t>
+          <t>larva, nymph, and adult</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>larva_and_nymph</t>
+          <t>forests</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>larva and nymph</t>
+          <t>forests</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>larva,_nymph,_and_adult</t>
+          <t>grasslands</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>larva, nymph, and adult</t>
+          <t>grasslands</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>forests</t>
+          <t>wetlands</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>forests</t>
+          <t>wetlands</t>
         </is>
       </c>
     </row>
@@ -1293,46 +1293,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>grasslands</t>
+          <t>deserts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>grasslands</t>
+          <t>deserts</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wetlands</t>
+          <t>deer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wetlands</t>
+          <t>Deer</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>deserts</t>
+          <t>rodents</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>deserts</t>
+          <t>Rodents</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>deer</t>
+          <t>humans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Deer</t>
+          <t>Humans</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rodents</t>
+          <t>horses</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rodents</t>
+          <t>Horses</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>humans</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Sheep</t>
         </is>
       </c>
     </row>
@@ -1395,46 +1395,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>horses</t>
+          <t>cattle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Horses</t>
+          <t>Cattle</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>lyme_disease</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sheep</t>
+          <t>Lyme disease</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cattle</t>
+          <t>tick-borne_anaplasmosis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>Tick-borne anaplasmosis</t>
         </is>
       </c>
     </row>
@@ -1446,46 +1446,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lyme_disease</t>
+          <t>tick-borne_relapsing_fever</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Tick-borne relapsing fever</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>tick-borne_anaplasmosis</t>
+          <t>larva</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tick-borne anaplasmosis</t>
+          <t>larva</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tick-borne_relapsing_fever</t>
+          <t>nymph</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tick-borne relapsing fever</t>
+          <t>nymph</t>
         </is>
       </c>
     </row>
@@ -1497,46 +1497,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>larva</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>larva</t>
+          <t>adult</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nymph</t>
+          <t>larva</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nymph</t>
+          <t>Larva</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>nymph</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>nymph</t>
         </is>
       </c>
     </row>
@@ -1548,46 +1548,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>larva</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Larva</t>
+          <t>adult</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nymph</t>
+          <t>forests</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nymph</t>
+          <t>forests</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>grasslands</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>grasslands</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>forests</t>
+          <t>wetlands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>forests</t>
+          <t>wetlands</t>
         </is>
       </c>
     </row>
@@ -1616,46 +1616,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>grasslands</t>
+          <t>deserts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>grasslands</t>
+          <t>deserts</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wetlands</t>
+          <t>lyme_disease</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wetlands</t>
+          <t>Lyme disease</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>deserts</t>
+          <t>tick-borne_anaplasmosis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>deserts</t>
+          <t>Tick-borne anaplasmosis</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>lyme_disease</t>
+          <t>tick-borne_relapsing_fever</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Tick-borne relapsing fever</t>
         </is>
       </c>
     </row>
@@ -1684,80 +1684,80 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tick-borne_anaplasmosis</t>
+          <t>tick-borne_babesiosis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tick-borne anaplasmosis</t>
+          <t>Tick-borne babesiosis</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tick-borne_relapsing_fever</t>
+          <t>to_educate</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tick-borne relapsing fever</t>
+          <t>to educate</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tick-borne_babesiosis</t>
+          <t>to_entertain</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tick-borne babesiosis</t>
+          <t>to entertain</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>to_educate</t>
+          <t>bite</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>to educate</t>
+          <t>bite</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>to_entertain</t>
+          <t>saliva</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>to entertain</t>
+          <t>saliva</t>
         </is>
       </c>
     </row>
@@ -1769,46 +1769,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>bite</t>
+          <t>feces</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bite</t>
+          <t>feces</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>saliva</t>
+          <t>forests</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>saliva</t>
+          <t>forests</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>feces</t>
+          <t>grasslands</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feces</t>
+          <t>grasslands</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>forests</t>
+          <t>wetlands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>forests</t>
+          <t>wetlands</t>
         </is>
       </c>
     </row>
@@ -1837,46 +1837,46 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>grasslands</t>
+          <t>deserts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>grasslands</t>
+          <t>deserts</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wetlands</t>
+          <t>lyme_disease</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>wetlands</t>
+          <t>Lyme disease</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>deserts</t>
+          <t>tick-borne_anaplasmosis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>deserts</t>
+          <t>Tick-borne anaplasmosis</t>
         </is>
       </c>
     </row>
@@ -1888,44 +1888,10 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>lyme_disease</t>
+          <t>tick-borne_relapsing_fever</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
-        <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>tick-borne_anaplasmosis</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tick-borne anaplasmosis</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>tick-borne_relapsing_fever</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
         <is>
           <t>Tick-borne relapsing fever</t>
         </is>
